--- a/Data/Rehires/Workday_Rehire_France_Regression_PK17.xlsx
+++ b/Data/Rehires/Workday_Rehire_France_Regression_PK17.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654120CE-CE09-4BB7-A270-290B139312C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Test_Data" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Test_Data" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="79">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -150,13 +136,19 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>France</t>
   </si>
   <si>
-    <t>Athena</t>
-  </si>
-  <si>
-    <t>Lesch</t>
+    <t>Maximus</t>
+  </si>
+  <si>
+    <t>Cartwright</t>
   </si>
   <si>
     <t>59700</t>
@@ -183,12 +175,12 @@
     <t>221 Paris-Villeneuve La Garenne</t>
   </si>
   <si>
+    <t>Employe@5 - Jeudi - (Contracted Days of the Week (France)-France)</t>
+  </si>
+  <si>
     <t>5 jours (France)</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Automation Comments here….</t>
   </si>
   <si>
@@ -231,10 +223,16 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>Roslyn</t>
+  </si>
+  <si>
+    <t>Simonis</t>
+  </si>
+  <si>
     <t>221 Store Management (Pucyw Zipato (9221018))</t>
   </si>
   <si>
-    <t>Auto 41715071</t>
+    <t>Auto 19607566</t>
   </si>
   <si>
     <t>Store Manager</t>
@@ -253,67 +251,61 @@
   </si>
   <si>
     <t>Test_4</t>
-  </si>
-  <si>
-    <t>Employe@5 - Jeudi - (Contracted Days of the Week (France)-France)</t>
-  </si>
-  <si>
-    <t>10699520</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
       <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF040C28"/>
+      <family val="2"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
+      <sz val="14"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color theme="10"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF040C28"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -331,7 +323,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -343,12 +335,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,39 +360,21 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -437,18 +411,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -468,8 +438,8 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -495,6 +465,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -775,9 +749,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BK5"/>
-  <sheetFormatPr defaultRowHeight="15.65" customHeight="1" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AM5"/>
+  <sheetFormatPr defaultRowHeight="15.65" outlineLevelRow="1" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" style="1" customWidth="1"/>
@@ -794,7 +768,7 @@
     <col min="13" max="13" width="13" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.6328125" style="2" customWidth="1"/>
     <col min="15" max="15" width="8.90625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.08984375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="28.36328125" style="1" customWidth="1"/>
     <col min="17" max="17" width="20.54296875" style="1" customWidth="1"/>
     <col min="18" max="18" width="31.08984375" style="1" customWidth="1"/>
     <col min="19" max="19" width="41.6328125" style="1" customWidth="1"/>
@@ -843,7 +817,7 @@
     <col min="64" max="64" width="16.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="1" customFormat="1" ht="14.5" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:39" s="1" customFormat="1" x14ac:dyDescent="0.25" outlineLevel="1" collapsed="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -962,286 +936,309 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="15.65" customHeight="1" spans="1:39" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>41</v>
+      </c>
       <c r="D2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="7">
+        <v>10699318</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="14" t="str">
+        <f>G2&amp;" "&amp;G2</f>
+        <v>Bruen Bruen</v>
+      </c>
+      <c r="K2" s="15">
+        <f>TODAY()-1</f>
+        <v>45867</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="19">
+        <v>35</v>
+      </c>
+      <c r="S2" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="V2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="W2" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="X2" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z2" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA2" s="15">
+        <f>K2+90</f>
+        <v>45957</v>
+      </c>
+      <c r="AB2" s="15">
+        <f>K2</f>
+        <v>45867</v>
+      </c>
+      <c r="AC2" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD2" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE2" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF2" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG2" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH2" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI2" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ2" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL2" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM2" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" ht="15.65" customHeight="1" spans="1:39" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="7">
+        <v>10699675</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="14" t="str">
+        <f>G3&amp;" "&amp;G3</f>
+        <v>Ziemann Ziemann</v>
+      </c>
+      <c r="K3" s="15">
+        <f>TODAY()-2</f>
+        <v>45866</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="R3" s="19">
+        <v>35</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="T3" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="V3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="W3" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="X3" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA3" s="15">
+        <f>K3+90</f>
+        <v>45956</v>
+      </c>
+      <c r="AB3" s="15">
+        <f>K3</f>
+        <v>45866</v>
+      </c>
+      <c r="AC3" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD3" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE3" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF3" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG3" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH3" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI3" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ3" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK3" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL3" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="12" t="s">
+      <c r="AM3" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" ht="15.65" customHeight="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="15" t="str">
-        <f>G2&amp;" "&amp;G2</f>
-        <v>Lesch Lesch</v>
-      </c>
-      <c r="K2" s="16">
-        <f ca="1">TODAY()-1</f>
-        <v>45854</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="R2" s="20">
-        <v>35</v>
-      </c>
-      <c r="S2" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="T2" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="U2" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="W2" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="X2" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y2" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z2" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA2" s="16">
-        <f ca="1">K2+90</f>
-        <v>45944</v>
-      </c>
-      <c r="AB2" s="16">
-        <f ca="1">K2</f>
-        <v>45854</v>
-      </c>
-      <c r="AC2" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD2" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE2" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF2" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG2" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH2" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI2" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ2" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK2" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL2" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="AM2" s="9" t="s">
-        <v>65</v>
-      </c>
+      <c r="H4" s="13"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="23"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="18"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="16"/>
+      <c r="Y4" s="16"/>
+      <c r="Z4" s="23"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="23"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="25"/>
+      <c r="AG4" s="26"/>
+      <c r="AH4" s="22"/>
+      <c r="AI4" s="22"/>
+      <c r="AJ4" s="22"/>
     </row>
-    <row r="3" spans="1:39" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="H3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J3" s="15" t="str">
-        <f>G3&amp;" "&amp;G3</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="K3" s="16">
-        <f ca="1">TODAY()-1</f>
-        <v>45854</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="R3" s="20">
-        <v>35</v>
-      </c>
-      <c r="S3" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="T3" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="U3" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="V3" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="X3" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="Y3" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z3" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA3" s="16">
-        <f ca="1">K3+90</f>
-        <v>45944</v>
-      </c>
-      <c r="AB3" s="16">
-        <f ca="1">K3</f>
-        <v>45854</v>
-      </c>
-      <c r="AC3" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD3" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE3" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF3" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="AG3" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH3" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI3" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ3" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="AK3" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL3" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="AM3" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:39" s="1" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="H4" s="14"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="24"/>
-      <c r="Q4" s="29"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="19"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="23"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="17"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="23"/>
-      <c r="AD4" s="25"/>
-      <c r="AE4" s="23"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="27"/>
-      <c r="AH4" s="23"/>
-      <c r="AI4" s="23"/>
-      <c r="AJ4" s="23"/>
-    </row>
-    <row r="5" spans="1:39" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.65" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="E5" s="30"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD4" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD4">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE3 L2:L3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4">
       <formula1>INDIRECT($F4)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L3">
+      <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 EXPLEO Internal</oddFooter>
   </headerFooter>
